--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="79">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -206,12 +206,6 @@
   </si>
   <si>
     <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE</t>
-  </si>
-  <si>
-    <t>OKREF03249 - {"path": "XWALTZ,XceleraCORE,XceleraSERVICE", "instance": "XceleraSERVICE", "symbol": "enable_ibias", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
@@ -634,7 +628,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -699,82 +693,72 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>41</v>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -789,7 +773,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -809,7 +793,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -824,7 +808,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -839,17 +823,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -151,100 +151,7 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -628,137 +535,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>72</v>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +560,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -793,7 +580,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -808,7 +595,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -823,17 +610,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>77</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1208,7 +995,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1218,42 +1005,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="79">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -151,7 +151,100 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -535,17 +628,137 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -560,7 +773,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -580,7 +793,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -595,7 +808,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -610,17 +823,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1005,7 +1218,42 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -9,24 +9,23 @@
   <sheets>
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
-    <sheet name="Missing Bio Symbol Files" sheetId="3" r:id="rId3"/>
-    <sheet name="Missing Nets" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Inputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Shorted Outputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Inputs" sheetId="7" r:id="rId7"/>
-    <sheet name="Floating Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Outputs" sheetId="9" r:id="rId9"/>
-    <sheet name="No Connects - Inputs" sheetId="10" r:id="rId10"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="11" r:id="rId11"/>
-    <sheet name="Ring Core IO check report" sheetId="12" r:id="rId12"/>
-    <sheet name="D to A Tree" sheetId="13" r:id="rId13"/>
+    <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
+    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
+    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
+    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
+    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
+    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
+    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -109,15 +108,6 @@
     <t>XWALTZ,XceleraCORE,XSOFTSTART</t>
   </si>
   <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>brick_acf9bbb6.bio</t>
-  </si>
-  <si>
-    <t>brick_acf9bbb6.v</t>
-  </si>
-  <si>
     <t>Missing Nets</t>
   </si>
   <si>
@@ -127,7 +117,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>No Shorted Input Nets found.</t>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
+  </si>
+  <si>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -151,100 +144,7 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -628,172 +528,32 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -808,32 +568,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>77</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1053,7 +813,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1071,33 +831,33 @@
         <v>28</v>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+    </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1183,7 +943,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1196,64 +956,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>48</v>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="333">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -117,10 +117,7 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>No Shorted Input Nets found.</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -132,7 +129,460 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_496698b1_XU8_be4c5eaa_XDEBUG(ten_496698b1_XU8_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_5e7931f3_XU7_be4c5eaa_XDEBUG(ten_5e7931f3_XU7_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7bb789c1_XU3_be4c5eaa_XDEBUG(ten_7bb789c1_XU3_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_bdb7126b_XU6_be4c5eaa_XDEBUG(ten_bdb7126b_XU6_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fc840bff_XU4_be4c5eaa_XDEBUG(ten_fc840bff_XU4_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_38b575fc_XU10_be4c5eaa_XDEBUG(ten_38b575fc_XU10_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_71505146_XU19_be4c5eaa_XDEBUG(ten_71505146_XU19_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_b20889dd_XU21_be4c5eaa_XDEBUG(ten_b20889dd_XU21_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f614d104_XU20_be4c5eaa_XDEBUG(ten_f614d104_XU20_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN(ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN(global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN(global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_016e5221_XU14_76edd7de_XCONTROL(ten_016e5221_XU14_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_10af5487_XU89_76edd7de_XCONTROL(ten_10af5487_XU89_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_1c924704_XU94_76edd7de_XCONTROL(ten_1c924704_XU94_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_250e1d7b_XU96_76edd7de_XCONTROL(ten_250e1d7b_XU96_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_3a54983a_XU93_76edd7de_XCONTROL(ten_3a54983a_XU93_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_5dbb5861_XU98_76edd7de_XCONTROL(ten_5dbb5861_XU98_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_78907f64_XU97_76edd7de_XCONTROL(ten_78907f64_XU97_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_9e0c6a0f_XU20_76edd7de_XCONTROL(ten_9e0c6a0f_XU20_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_a9541403_XU99_76edd7de_XCONTROL(ten_a9541403_XU99_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_b275df66_XU92_76edd7de_XCONTROL(ten_b275df66_XU92_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_c406e2e9_XU16_76edd7de_XCONTROL(ten_c406e2e9_XU16_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_dc7df0cc_XU18_76edd7de_XCONTROL(ten_dc7df0cc_XU18_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e1c50519_XU90_76edd7de_XCONTROL(ten_e1c50519_XU90_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e41e5cb3_XU95_76edd7de_XCONTROL(ten_e41e5cb3_XU95_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_efe3dfd4_XU91_76edd7de_XCONTROL(ten_efe3dfd4_XU91_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW(global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_2a0216d2_XU20_c1b82e6f_XDEBUG(ten_2a0216d2_XU20_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_32f97a89_XU11_c1b82e6f_XDEBUG(ten_32f97a89_XU11_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_34071f1d_XU15_c1b82e6f_XDEBUG(ten_34071f1d_XU15_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_3788e0aa_XU16_c1b82e6f_XDEBUG(ten_3788e0aa_XU16_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_e5798d25_XU18_c1b82e6f_XDEBUG(ten_e5798d25_XU18_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f83f6ba2_XU10_c1b82e6f_XDEBUG(ten_f83f6ba2_XU10_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fcfb2c12_XU12_c1b82e6f_XDEBUG(ten_fcfb2c12_XU12_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_af379456_XU5_c1b82e6f_XDEBUG(ten_hijack_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG(ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_cboot_35156756_XU17_f604d85e_XTOPSW(global_cboot_35156756_XU17_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW(global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW(ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW(global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW(ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6044b743_XU7_4c867da6_XDEBUG(ten_6044b743_XU7_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e48a0c0_XU2_4c867da6_XDEBUG(ten_7e48a0c0_XU2_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e6d3e04_XU1_4c867da6_XDEBUG(ten_7e6d3e04_XU1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_0b40c959_XU6_4c867da6_XDEBUG(ten_hijack_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_54e727e4_XU15_4c867da6_XDEBUG(ten_hijack_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9929432d_XU17_4c867da6_XDEBUG(ten_hijack_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG(ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG(ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9929432d_XU17_4c867da6_XDEBUG(ten_hijacki_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN(ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_14c9168a_XU7_1cec7299_XDEBUG(ten_14c9168a_XU7_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6d67c253_XU1_1cec7299_XDEBUG(ten_6d67c253_XU1_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_c69fe1aa_XU8_1cec7299_XDEBUG(ten_c69fe1aa_XU8_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1d78f0e4_XU13_1cec7299_XDEBUG(ten_1d78f0e4_XU13_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d748b831_XU15_1cec7299_XDEBUG(ten_d748b831_XU15_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f4762d45_XU11_1cec7299_XDEBUG(ten_f4762d45_XU11_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_6613b2af_XU3_1cec7299_XDEBUG(ten_hijack_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c541f94b_XU16_1cec7299_XDEBUG(ten_hijack_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG(ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG(ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG(ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_e96a4067_XU8_811a9a05_XMAIN(global_vbuffer_e96a4067_XU8_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN(ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_70e67769_XU3_811a9a05_XMAIN(global_comparator_70e67769_XU3_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_ddbf938d_XU22_811a9a05_XMAIN(global_comparator_ddbf938d_XU22_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_resistordivider_37d49b79_XU17_811a9a05_XMAIN(global_resistordivider_37d49b79_XU17_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_162b659f_XU9_f255c70e_XDEBUG(ten_162b659f_XU9_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_83ff2716_XU8_f255c70e_XDEBUG(ten_83ff2716_XU8_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_913fa695_XU7_f255c70e_XDEBUG(ten_913fa695_XU7_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_95483466_XU2_f255c70e_XDEBUG(ten_95483466_XU2_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d922ca5f_XU6_f255c70e_XDEBUG(ten_d922ca5f_XU6_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_de422ccd_XU11_f255c70e_XDEBUG(ten_hijack_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG(ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_gm_e44d2b4d_Xgm1_10783060_XMAIN(global_gm_e44d2b4d_Xgm1_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clamp_b8eb1a18_XU7_10783060_XMAIN(global_clamp_b8eb1a18_XU7_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_866ca25c_XU9_10783060_XMAIN(global_vbuffer_866ca25c_XU9_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_5c7dff44_XU10_10783060_XMAIN(global_comparator_5c7dff44_XU10_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_voltage2current_4215aede_XU3_10783060_XMAIN(global_voltage2current_4215aede_XU3_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_0721e5d9_XU56_5c792007_XSEQUENCER(ten_0721e5d9_XU56_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_2958f818_XU61_5c792007_XSEQUENCER(ten_2958f818_XU61_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_29fa69a5_XU60_5c792007_XSEQUENCER(ten_29fa69a5_XU60_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_3bd9bacc_XU59_5c792007_XSEQUENCER(ten_3bd9bacc_XU59_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_445acf01_XU57_5c792007_XSEQUENCER(ten_445acf01_XU57_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4c7ada73_XU65_5c792007_XSEQUENCER(ten_4c7ada73_XU65_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4d227e72_XU55_5c792007_XSEQUENCER(ten_4d227e72_XU55_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_6cd23b02_XU66_5c792007_XSEQUENCER(ten_6cd23b02_XU66_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_70525239_XU58_5c792007_XSEQUENCER(ten_70525239_XU58_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_950364d7_XU54_5c792007_XSEQUENCER(ten_950364d7_XU54_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9d829c39_XU62_5c792007_XSEQUENCER(ten_9d829c39_XU62_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9ef032e9_XU63_5c792007_XSEQUENCER(ten_9ef032e9_XU63_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_e8d90cd0_XU64_5c792007_XSEQUENCER(ten_e8d90cd0_XU64_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1955111b_XU7_63f6e3c4_XDEBUG(ten_1955111b_XU7_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_742857bf_XU2_63f6e3c4_XDEBUG(ten_742857bf_XU2_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_a6a0ac97_XU3_63f6e3c4_XDEBUG(ten_a6a0ac97_XU3_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ec5776d4_XU6_63f6e3c4_XDEBUG(ten_ec5776d4_XU6_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_cd882763_XU15_63f6e3c4_XDEBUG(ten_cd882763_XU15_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_ref_553d3e5b_XU4_2345cd7b_XMAIN(ten_ref_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN(ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_reference_553d3e5b_XU4_2345cd7b_XMAIN(global_reference_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN(global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_75c89176_XU16_2345cd7b_XMAIN(global_comparator_75c89176_XU16_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_81f80d4d_XU8_88e49508_XDEBUG(ten_81f80d4d_XU8_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ed87e5db_XU5_88e49508_XDEBUG(ten_ed87e5db_XU5_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f665b623_XU6_88e49508_XDEBUG(ten_f665b623_XU6_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_528f048c_XU10_88e49508_XDEBUG(ten_528f048c_XU10_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_297df8ef_XU1_88e49508_XDEBUG(ten_hijack_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_dcf795e2_XU14_88e49508_XDEBUG(ten_hijack_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_297df8ef_XU1_88e49508_XDEBUG(ten_hijacki_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG(ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_dac_0cc08401_XU5_b48f6491_XMAIN8(global_dac_0cc08401_XU5_b48f6491_XMAIN8)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8(global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -147,6 +597,420 @@
     <t>No Connects - Inputs</t>
   </si>
   <si>
+    <t>ten_496698b1_XU8_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_496698b1_XU8_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5e7931f3_XU7_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_5e7931f3_XU7_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7bb789c1_XU3_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7bb789c1_XU3_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_bdb7126b_XU6_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_bdb7126b_XU6_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fc840bff_XU4_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fc840bff_XU4_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_38b575fc_XU10_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_38b575fc_XU10_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_71505146_XU19_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_71505146_XU19_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b20889dd_XU21_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_b20889dd_XU21_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f614d104_XU20_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f614d104_XU20_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_016e5221_XU14_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_016e5221_XU14_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_10af5487_XU89_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_10af5487_XU89_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1c924704_XU94_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_1c924704_XU94_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_250e1d7b_XU96_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_250e1d7b_XU96_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3a54983a_XU93_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_3a54983a_XU93_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5dbb5861_XU98_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_5dbb5861_XU98_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_78907f64_XU97_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_78907f64_XU97_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9e0c6a0f_XU20_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_9e0c6a0f_XU20_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a9541403_XU99_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_a9541403_XU99_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b275df66_XU92_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_b275df66_XU92_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c406e2e9_XU16_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_c406e2e9_XU16_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_dc7df0cc_XU18_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_dc7df0cc_XU18_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e1c50519_XU90_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e1c50519_XU90_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e41e5cb3_XU95_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e41e5cb3_XU95_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_efe3dfd4_XU91_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_efe3dfd4_XU91_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2a0216d2_XU20_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_2a0216d2_XU20_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_32f97a89_XU11_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_32f97a89_XU11_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_34071f1d_XU15_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_34071f1d_XU15_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3788e0aa_XU16_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_3788e0aa_XU16_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e5798d25_XU18_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_e5798d25_XU18_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f83f6ba2_XU10_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f83f6ba2_XU10_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fcfb2c12_XU12_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fcfb2c12_XU12_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_cboot_35156756_XU17_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_cboot_35156756_XU17_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6044b743_XU7_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6044b743_XU7_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e48a0c0_XU2_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e48a0c0_XU2_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e6d3e04_XU1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e6d3e04_XU1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_14c9168a_XU7_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_14c9168a_XU7_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6d67c253_XU1_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6d67c253_XU1_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c69fe1aa_XU8_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_c69fe1aa_XU8_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1d78f0e4_XU13_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1d78f0e4_XU13_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d748b831_XU15_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d748b831_XU15_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f4762d45_XU11_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f4762d45_XU11_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_e96a4067_XU8_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_e96a4067_XU8_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_70e67769_XU3_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_70e67769_XU3_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_ddbf938d_XU22_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_ddbf938d_XU22_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_resistordivider_37d49b79_XU17_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_162b659f_XU9_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_162b659f_XU9_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_83ff2716_XU8_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_83ff2716_XU8_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_913fa695_XU7_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_913fa695_XU7_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_95483466_XU2_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_95483466_XU2_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d922ca5f_XU6_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d922ca5f_XU6_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_gm_e44d2b4d_Xgm1_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_gm_e44d2b4d_Xgm1_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clamp_b8eb1a18_XU7_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_clamp_b8eb1a18_XU7_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_866ca25c_XU9_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_866ca25c_XU9_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_5c7dff44_XU10_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_5c7dff44_XU10_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_voltage2current_4215aede_XU3_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_voltage2current_4215aede_XU3_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_0721e5d9_XU56_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_0721e5d9_XU56_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2958f818_XU61_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_2958f818_XU61_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_29fa69a5_XU60_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_29fa69a5_XU60_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3bd9bacc_XU59_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_3bd9bacc_XU59_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_445acf01_XU57_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_445acf01_XU57_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4c7ada73_XU65_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4c7ada73_XU65_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4d227e72_XU55_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4d227e72_XU55_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6cd23b02_XU66_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_6cd23b02_XU66_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_70525239_XU58_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_70525239_XU58_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_950364d7_XU54_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_950364d7_XU54_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9d829c39_XU62_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9d829c39_XU62_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9ef032e9_XU63_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9ef032e9_XU63_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e8d90cd0_XU64_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_e8d90cd0_XU64_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1955111b_XU7_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1955111b_XU7_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_742857bf_XU2_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_742857bf_XU2_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a6a0ac97_XU3_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_a6a0ac97_XU3_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ec5776d4_XU6_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ec5776d4_XU6_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_cd882763_XU15_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_cd882763_XU15_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ref_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_ref_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_reference_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_reference_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_75c89176_XU16_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_75c89176_XU16_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_81f80d4d_XU8_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_81f80d4d_XU8_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ed87e5db_XU5_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ed87e5db_XU5_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f665b623_XU6_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f665b623_XU6_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_528f048c_XU10_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_528f048c_XU10_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_dac_0cc08401_XU5_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_dac_0cc08401_XU5_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -157,9 +1021,6 @@
   </si>
   <si>
     <t>D to A Tree</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
     <t>Xoscillator1</t>
@@ -533,7 +1394,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -553,7 +1414,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -568,7 +1429,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -583,17 +1444,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -848,17 +1709,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -873,7 +1729,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -883,7 +1739,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -893,12 +1749,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -908,7 +1764,782 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +2554,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -933,7 +2564,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +2579,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -963,17 +2594,787 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="457">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -117,7 +117,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>No Shorted Input Nets found.</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -129,21 +132,1257 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_496698b1_XU8_be4c5eaa_XDEBUG(ten_496698b1_XU8_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_5e7931f3_XU7_be4c5eaa_XDEBUG(ten_5e7931f3_XU7_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7bb789c1_XU3_be4c5eaa_XDEBUG(ten_7bb789c1_XU3_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_bdb7126b_XU6_be4c5eaa_XDEBUG(ten_bdb7126b_XU6_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fc840bff_XU4_be4c5eaa_XDEBUG(ten_fc840bff_XU4_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_38b575fc_XU10_be4c5eaa_XDEBUG(ten_38b575fc_XU10_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_71505146_XU19_be4c5eaa_XDEBUG(ten_71505146_XU19_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_b20889dd_XU21_be4c5eaa_XDEBUG(ten_b20889dd_XU21_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f614d104_XU20_be4c5eaa_XDEBUG(ten_f614d104_XU20_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN(ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN(global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN(global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_016e5221_XU14_76edd7de_XCONTROL(ten_016e5221_XU14_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_10af5487_XU89_76edd7de_XCONTROL(ten_10af5487_XU89_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_1c924704_XU94_76edd7de_XCONTROL(ten_1c924704_XU94_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_250e1d7b_XU96_76edd7de_XCONTROL(ten_250e1d7b_XU96_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_3a54983a_XU93_76edd7de_XCONTROL(ten_3a54983a_XU93_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_5dbb5861_XU98_76edd7de_XCONTROL(ten_5dbb5861_XU98_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_78907f64_XU97_76edd7de_XCONTROL(ten_78907f64_XU97_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_9e0c6a0f_XU20_76edd7de_XCONTROL(ten_9e0c6a0f_XU20_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_a9541403_XU99_76edd7de_XCONTROL(ten_a9541403_XU99_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_b275df66_XU92_76edd7de_XCONTROL(ten_b275df66_XU92_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_c406e2e9_XU16_76edd7de_XCONTROL(ten_c406e2e9_XU16_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_dc7df0cc_XU18_76edd7de_XCONTROL(ten_dc7df0cc_XU18_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e1c50519_XU90_76edd7de_XCONTROL(ten_e1c50519_XU90_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e41e5cb3_XU95_76edd7de_XCONTROL(ten_e41e5cb3_XU95_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_efe3dfd4_XU91_76edd7de_XCONTROL(ten_efe3dfd4_XU91_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW(global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_2a0216d2_XU20_c1b82e6f_XDEBUG(ten_2a0216d2_XU20_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_32f97a89_XU11_c1b82e6f_XDEBUG(ten_32f97a89_XU11_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_34071f1d_XU15_c1b82e6f_XDEBUG(ten_34071f1d_XU15_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_3788e0aa_XU16_c1b82e6f_XDEBUG(ten_3788e0aa_XU16_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_e5798d25_XU18_c1b82e6f_XDEBUG(ten_e5798d25_XU18_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f83f6ba2_XU10_c1b82e6f_XDEBUG(ten_f83f6ba2_XU10_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fcfb2c12_XU12_c1b82e6f_XDEBUG(ten_fcfb2c12_XU12_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_af379456_XU5_c1b82e6f_XDEBUG(ten_hijack_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG(ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_cboot_35156756_XU17_f604d85e_XTOPSW(global_cboot_35156756_XU17_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW(global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW(ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW(global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW(ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6044b743_XU7_4c867da6_XDEBUG(ten_6044b743_XU7_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e48a0c0_XU2_4c867da6_XDEBUG(ten_7e48a0c0_XU2_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e6d3e04_XU1_4c867da6_XDEBUG(ten_7e6d3e04_XU1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_0b40c959_XU6_4c867da6_XDEBUG(ten_hijack_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_54e727e4_XU15_4c867da6_XDEBUG(ten_hijack_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9929432d_XU17_4c867da6_XDEBUG(ten_hijack_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG(ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG(ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9929432d_XU17_4c867da6_XDEBUG(ten_hijacki_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN(ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_14c9168a_XU7_1cec7299_XDEBUG(ten_14c9168a_XU7_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6d67c253_XU1_1cec7299_XDEBUG(ten_6d67c253_XU1_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_c69fe1aa_XU8_1cec7299_XDEBUG(ten_c69fe1aa_XU8_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1d78f0e4_XU13_1cec7299_XDEBUG(ten_1d78f0e4_XU13_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d748b831_XU15_1cec7299_XDEBUG(ten_d748b831_XU15_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f4762d45_XU11_1cec7299_XDEBUG(ten_f4762d45_XU11_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_6613b2af_XU3_1cec7299_XDEBUG(ten_hijack_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c541f94b_XU16_1cec7299_XDEBUG(ten_hijack_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG(ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG(ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG(ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_e96a4067_XU8_811a9a05_XMAIN(global_vbuffer_e96a4067_XU8_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN(ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_70e67769_XU3_811a9a05_XMAIN(global_comparator_70e67769_XU3_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_ddbf938d_XU22_811a9a05_XMAIN(global_comparator_ddbf938d_XU22_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_resistordivider_37d49b79_XU17_811a9a05_XMAIN(global_resistordivider_37d49b79_XU17_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_162b659f_XU9_f255c70e_XDEBUG(ten_162b659f_XU9_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_83ff2716_XU8_f255c70e_XDEBUG(ten_83ff2716_XU8_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_913fa695_XU7_f255c70e_XDEBUG(ten_913fa695_XU7_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_95483466_XU2_f255c70e_XDEBUG(ten_95483466_XU2_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d922ca5f_XU6_f255c70e_XDEBUG(ten_d922ca5f_XU6_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_de422ccd_XU11_f255c70e_XDEBUG(ten_hijack_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG(ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_gm_e44d2b4d_Xgm1_10783060_XMAIN(global_gm_e44d2b4d_Xgm1_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clamp_b8eb1a18_XU7_10783060_XMAIN(global_clamp_b8eb1a18_XU7_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_866ca25c_XU9_10783060_XMAIN(global_vbuffer_866ca25c_XU9_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_5c7dff44_XU10_10783060_XMAIN(global_comparator_5c7dff44_XU10_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_voltage2current_4215aede_XU3_10783060_XMAIN(global_voltage2current_4215aede_XU3_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_0721e5d9_XU56_5c792007_XSEQUENCER(ten_0721e5d9_XU56_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_2958f818_XU61_5c792007_XSEQUENCER(ten_2958f818_XU61_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_29fa69a5_XU60_5c792007_XSEQUENCER(ten_29fa69a5_XU60_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_3bd9bacc_XU59_5c792007_XSEQUENCER(ten_3bd9bacc_XU59_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_445acf01_XU57_5c792007_XSEQUENCER(ten_445acf01_XU57_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4c7ada73_XU65_5c792007_XSEQUENCER(ten_4c7ada73_XU65_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4d227e72_XU55_5c792007_XSEQUENCER(ten_4d227e72_XU55_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_6cd23b02_XU66_5c792007_XSEQUENCER(ten_6cd23b02_XU66_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_70525239_XU58_5c792007_XSEQUENCER(ten_70525239_XU58_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_950364d7_XU54_5c792007_XSEQUENCER(ten_950364d7_XU54_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9d829c39_XU62_5c792007_XSEQUENCER(ten_9d829c39_XU62_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9ef032e9_XU63_5c792007_XSEQUENCER(ten_9ef032e9_XU63_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_e8d90cd0_XU64_5c792007_XSEQUENCER(ten_e8d90cd0_XU64_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1955111b_XU7_63f6e3c4_XDEBUG(ten_1955111b_XU7_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_742857bf_XU2_63f6e3c4_XDEBUG(ten_742857bf_XU2_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_a6a0ac97_XU3_63f6e3c4_XDEBUG(ten_a6a0ac97_XU3_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ec5776d4_XU6_63f6e3c4_XDEBUG(ten_ec5776d4_XU6_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_cd882763_XU15_63f6e3c4_XDEBUG(ten_cd882763_XU15_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_ref_553d3e5b_XU4_2345cd7b_XMAIN(ten_ref_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN(ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_reference_553d3e5b_XU4_2345cd7b_XMAIN(global_reference_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN(global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_75c89176_XU16_2345cd7b_XMAIN(global_comparator_75c89176_XU16_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_81f80d4d_XU8_88e49508_XDEBUG(ten_81f80d4d_XU8_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ed87e5db_XU5_88e49508_XDEBUG(ten_ed87e5db_XU5_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f665b623_XU6_88e49508_XDEBUG(ten_f665b623_XU6_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_528f048c_XU10_88e49508_XDEBUG(ten_528f048c_XU10_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_297df8ef_XU1_88e49508_XDEBUG(ten_hijack_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_dcf795e2_XU14_88e49508_XDEBUG(ten_hijack_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_297df8ef_XU1_88e49508_XDEBUG(ten_hijacki_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG(ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_dac_0cc08401_XU5_b48f6491_XMAIN8(global_dac_0cc08401_XU5_b48f6491_XMAIN8)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8(global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
   </si>
   <si>
+    <t>ten_496698b1_XU8_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_496698b1_XU8_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5e7931f3_XU7_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_5e7931f3_XU7_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7bb789c1_XU3_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7bb789c1_XU3_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_bdb7126b_XU6_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_bdb7126b_XU6_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fc840bff_XU4_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fc840bff_XU4_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_38b575fc_XU10_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_38b575fc_XU10_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_71505146_XU19_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_71505146_XU19_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b20889dd_XU21_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_b20889dd_XU21_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f614d104_XU20_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f614d104_XU20_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>ten_016e5221_XU14_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_016e5221_XU14_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_10af5487_XU89_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_10af5487_XU89_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1c924704_XU94_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_1c924704_XU94_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_250e1d7b_XU96_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_250e1d7b_XU96_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3a54983a_XU93_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_3a54983a_XU93_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5dbb5861_XU98_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_5dbb5861_XU98_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_78907f64_XU97_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_78907f64_XU97_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9e0c6a0f_XU20_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_9e0c6a0f_XU20_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a9541403_XU99_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_a9541403_XU99_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b275df66_XU92_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_b275df66_XU92_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c406e2e9_XU16_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_c406e2e9_XU16_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_dc7df0cc_XU18_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_dc7df0cc_XU18_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e1c50519_XU90_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e1c50519_XU90_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e41e5cb3_XU95_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e41e5cb3_XU95_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_efe3dfd4_XU91_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_efe3dfd4_XU91_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2a0216d2_XU20_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_2a0216d2_XU20_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_32f97a89_XU11_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_32f97a89_XU11_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_34071f1d_XU15_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_34071f1d_XU15_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3788e0aa_XU16_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_3788e0aa_XU16_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e5798d25_XU18_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_e5798d25_XU18_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f83f6ba2_XU10_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f83f6ba2_XU10_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fcfb2c12_XU12_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fcfb2c12_XU12_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_cboot_35156756_XU17_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_cboot_35156756_XU17_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_6044b743_XU7_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6044b743_XU7_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e48a0c0_XU2_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e48a0c0_XU2_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e6d3e04_XU1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e6d3e04_XU1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>ten_14c9168a_XU7_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_14c9168a_XU7_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6d67c253_XU1_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6d67c253_XU1_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c69fe1aa_XU8_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_c69fe1aa_XU8_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1d78f0e4_XU13_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1d78f0e4_XU13_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d748b831_XU15_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d748b831_XU15_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f4762d45_XU11_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f4762d45_XU11_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_e96a4067_XU8_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_e96a4067_XU8_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_70e67769_XU3_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_70e67769_XU3_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_ddbf938d_XU22_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_ddbf938d_XU22_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_resistordivider_37d49b79_XU17_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_162b659f_XU9_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_162b659f_XU9_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_83ff2716_XU8_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_83ff2716_XU8_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_913fa695_XU7_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_913fa695_XU7_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_95483466_XU2_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_95483466_XU2_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d922ca5f_XU6_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d922ca5f_XU6_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>global_gm_e44d2b4d_Xgm1_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_gm_e44d2b4d_Xgm1_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clamp_b8eb1a18_XU7_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_clamp_b8eb1a18_XU7_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_866ca25c_XU9_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_866ca25c_XU9_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_5c7dff44_XU10_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_5c7dff44_XU10_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_voltage2current_4215aede_XU3_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_voltage2current_4215aede_XU3_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_0721e5d9_XU56_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_0721e5d9_XU56_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2958f818_XU61_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_2958f818_XU61_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_29fa69a5_XU60_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_29fa69a5_XU60_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3bd9bacc_XU59_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_3bd9bacc_XU59_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_445acf01_XU57_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_445acf01_XU57_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4c7ada73_XU65_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4c7ada73_XU65_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4d227e72_XU55_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4d227e72_XU55_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6cd23b02_XU66_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_6cd23b02_XU66_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_70525239_XU58_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_70525239_XU58_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_950364d7_XU54_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_950364d7_XU54_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9d829c39_XU62_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9d829c39_XU62_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9ef032e9_XU63_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9ef032e9_XU63_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e8d90cd0_XU64_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_e8d90cd0_XU64_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>ten_1955111b_XU7_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1955111b_XU7_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_742857bf_XU2_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_742857bf_XU2_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a6a0ac97_XU3_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_a6a0ac97_XU3_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ec5776d4_XU6_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ec5776d4_XU6_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_cd882763_XU15_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_cd882763_XU15_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ref_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_ref_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_reference_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_reference_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_75c89176_XU16_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_75c89176_XU16_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_81f80d4d_XU8_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_81f80d4d_XU8_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ed87e5db_XU5_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ed87e5db_XU5_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f665b623_XU6_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f665b623_XU6_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_528f048c_XU10_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_528f048c_XU10_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_dac_0cc08401_XU5_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_dac_0cc08401_XU5_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -154,9 +1393,6 @@
   </si>
   <si>
     <t>D to A Tree</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
     <t>Xoscillator1</t>
@@ -530,7 +1766,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -550,7 +1786,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -565,7 +1801,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -580,17 +1816,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +2071,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -845,12 +2081,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -865,7 +2106,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -875,7 +2116,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -885,12 +2126,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -900,7 +2141,1082 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -910,22 +3226,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -935,17 +3281,52 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -955,17 +3336,1097 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="134">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -117,10 +117,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -132,7 +132,142 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraCORE.PORB97836(PORB97836)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -145,6 +280,135 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>PORB97836 - {"path": "XWALTZ,XceleraCORE", "instance": "XceleraCORE", "symbol": "PORB97836", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -533,7 +797,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -553,7 +817,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -568,7 +832,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -583,17 +847,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -893,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -909,6 +1173,276 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +1457,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -933,7 +1467,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +1482,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -963,17 +1497,282 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -117,10 +117,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
-  </si>
-  <si>
-    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
+  </si>
+  <si>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -132,142 +132,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.fcm(59)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_bottom(60)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_refresh(61)</t>
-  </si>
-  <si>
-    <t>Floating pin XU21.i0(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU22.i0(49)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XU11.enable_switchb(102)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.mode_hiccup(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.blank_thermal(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XU10.enable_switch(58)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(35)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(34)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(33)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(49)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.halfway(36)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
-  </si>
-  <si>
-    <t>XWALTZ</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraCORE.PORB97836(PORB97836)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -280,135 +145,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>PORB97836 - {"path": "XWALTZ,XceleraCORE", "instance": "XceleraCORE", "symbol": "PORB97836", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -797,7 +533,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -817,7 +553,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -832,7 +568,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -847,17 +583,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1157,7 +893,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1175,289 +911,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1467,7 +933,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +948,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1497,282 +963,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A67"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>127</v>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="169">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -117,10 +117,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -132,19 +132,388 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -533,7 +902,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -553,7 +922,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -568,7 +937,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -583,17 +952,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -893,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -909,6 +1278,326 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -918,22 +1607,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -943,17 +1662,52 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -963,17 +1717,342 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="176">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -210,6 +210,18 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.VSENSE(105)</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.IREPLICA(100)</t>
+  </si>
+  <si>
+    <t>Floating pin XNC66.noconn(66)</t>
+  </si>
+  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -267,22 +279,22 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+    <t>Floating pin XSERDESdftNoNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otpdone(otp_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_pgenb(otp_pgenb)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_clock_enable(otp_clock_enable)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
@@ -303,22 +315,22 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftNoNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
@@ -327,22 +339,22 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
@@ -423,6 +435,15 @@
     <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
   </si>
   <si>
+    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -483,22 +504,22 @@
     <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_pgenb - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_pgenb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -902,7 +923,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -922,7 +943,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -937,7 +958,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -952,17 +973,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1422,132 +1443,132 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
+      <c r="A53" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
+      <c r="A63" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
+      <c r="A68" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -1561,43 +1582,63 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1612,47 +1653,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1667,47 +1708,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1717,12 +1758,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1732,22 +1773,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1757,27 +1798,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1787,17 +1828,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1807,252 +1848,272 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>140</v>
+      <c r="A50" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
+      <c r="A55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
+      <c r="A60" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>150</v>
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>154</v>
+      <c r="A70" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>162</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="159">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -210,18 +210,6 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.VSENSE(105)</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.IREPLICA(100)</t>
-  </si>
-  <si>
-    <t>Floating pin XNC66.noconn(66)</t>
-  </si>
-  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -303,15 +291,6 @@
     <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
   </si>
   <si>
-    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
-  </si>
-  <si>
     <t>Floating Outputs</t>
   </si>
   <si>
@@ -333,9 +312,6 @@
     <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
-    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
-  </si>
-  <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
@@ -357,9 +333,6 @@
     <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
   </si>
   <si>
@@ -435,15 +408,6 @@
     <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
   </si>
   <si>
-    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -498,12 +462,6 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
     <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -526,15 +484,6 @@
   </si>
   <si>
     <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -923,7 +872,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -943,7 +892,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -958,7 +907,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -973,17 +922,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -1283,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A85"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1443,132 +1392,132 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="1" t="s">
-        <v>19</v>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>73</v>
+      <c r="A58" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>77</v>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -1582,63 +1531,28 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1648,52 +1562,47 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1703,52 +1612,47 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1758,12 +1662,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1773,22 +1677,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1798,27 +1702,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1828,17 +1732,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1848,272 +1752,227 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>138</v>
+      <c r="A38" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>16</v>
+      <c r="A40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>17</v>
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>141</v>
+      <c r="A45" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>18</v>
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>19</v>
+      <c r="A50" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>147</v>
+      <c r="A55" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>151</v>
+      <c r="A60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>26</v>
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="1" t="s">
-        <v>83</v>
+      <c r="A70" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -267,22 +267,22 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftNoNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otpdone(otp_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_pgenb(otp_pgenb)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_clock_enable(otp_clock_enable)</t>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
@@ -294,43 +294,43 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftNoNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -462,22 +462,22 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_pgenb - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_pgenb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="139">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -267,24 +267,9 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
     <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
   </si>
   <si>
@@ -294,43 +279,13 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftYesNo.tdo(tdo_noconn)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdo_noconn - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdo", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -462,22 +417,7 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -872,7 +812,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -892,7 +832,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -907,7 +847,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -922,17 +862,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1232,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A77"/>
+  <dimension ref="A1:A72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1528,31 +1468,6 @@
     <row r="72" spans="1:1">
       <c r="A72" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1562,12 +1477,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1577,32 +1492,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1612,12 +1502,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1627,32 +1517,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1662,12 +1527,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1677,22 +1542,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1702,27 +1567,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1732,17 +1597,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1752,62 +1617,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -1817,7 +1682,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -1827,12 +1692,12 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -1842,7 +1707,7 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1852,42 +1717,42 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -1897,22 +1762,22 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -1922,12 +1787,12 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -1937,42 +1802,17 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="138">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -279,13 +279,10 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdo(tdo_noconn)</t>
+    <t>No Floating Output Nets found.</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>tdo_noconn - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdo", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -812,7 +809,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -832,7 +829,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -847,7 +844,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -862,17 +859,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1487,7 +1484,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1502,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1512,12 +1509,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1524,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1542,22 +1534,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1567,27 +1559,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1597,17 +1589,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1617,62 +1609,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -1682,7 +1674,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -1692,12 +1684,12 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -1707,7 +1699,7 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1717,42 +1709,42 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -1762,22 +1754,22 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -1787,12 +1779,12 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -1802,17 +1794,17 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="111">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -180,36 +180,6 @@
     <t>Floating pin XU22.i0(49)</t>
   </si>
   <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
-  </si>
-  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -264,18 +234,6 @@
     <t>Floating pin XMAIN8.softstart_1ms(35)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
-  </si>
-  <si>
     <t>Floating Outputs</t>
   </si>
   <si>
@@ -330,36 +288,6 @@
     <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -412,15 +340,6 @@
   </si>
   <si>
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -809,7 +728,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -829,7 +748,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -844,7 +763,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -859,17 +778,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1169,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A72"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1278,193 +1197,123 @@
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>52</v>
+      <c r="A28" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>55</v>
+      <c r="A31" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>59</v>
+      <c r="A35" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
+      <c r="A41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>18</v>
+      <c r="A45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>70</v>
+      <c r="A54" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1479,7 +1328,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1489,7 +1338,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +1353,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1519,12 +1368,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1534,22 +1383,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1559,27 +1408,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1589,17 +1438,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1609,202 +1458,132 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>102</v>
+      <c r="A25" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>105</v>
+      <c r="A28" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>109</v>
+      <c r="A32" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>18</v>
+      <c r="A42" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>120</v>
+      <c r="A51" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -117,12 +117,36 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XMAIN.CLOCKofftime_0 --&gt; XMAIN.CLOCKofftime_1 --&gt; XMAIN.CLOCKofftime_2 --&gt; XMAIN.CLOCKofftime_3(a0)</t>
+  </si>
+  <si>
+    <t>Shorted input d0 XALGORITHM.enableFAULT --&gt; XALGORITHM.STATEcontrol0 --&gt; XALGORITHM.STATEcontrol1 --&gt; XALGORITHM.STATEcontrol2 --&gt; XALGORITHM.STATEcontrol3(d0)</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XCONTROL.fcm --&gt; XCONTROL.blank_bottom --&gt; XCONTROL.blank_refresh(a0)</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XU21.i0 --&gt; XU22.i0(a0)</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XMAIN.mode_hiccup --&gt; XMAIN.blank_thermal(a0)</t>
+  </si>
+  <si>
     <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
   </si>
   <si>
     <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
+    <t>Shorted input d0 XMAIN.STATEcontrol0 --&gt; XMAIN.STATEcontrol1 --&gt; XMAIN.STATEcontrol2 --&gt; XMAIN.STATEcontrol3(d0)</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XMAIN8.halfway --&gt; XMAIN8.softstart_1ms(a0)</t>
+  </si>
+  <si>
     <t>Shorted Outputs</t>
   </si>
   <si>
@@ -132,106 +156,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.fcm(59)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_bottom(60)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_refresh(61)</t>
-  </si>
-  <si>
-    <t>Floating pin XU21.i0(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU22.i0(49)</t>
-  </si>
-  <si>
-    <t>Floating pin XU11.enable_switchb(102)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.mode_hiccup(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.blank_thermal(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XU10.enable_switch(58)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(35)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(34)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(33)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(49)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.halfway(36)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -244,102 +169,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -728,7 +557,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -748,7 +577,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -763,7 +592,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -778,17 +607,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>109</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +862,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1043,17 +872,87 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>31</v>
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +967,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1078,7 +977,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1088,12 +987,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1103,232 +1002,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1338,7 +1027,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1042,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1368,222 +1057,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A54"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>104</v>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="61">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -156,7 +156,19 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.VSENSE(105)</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.IREPLICA(100)</t>
+  </si>
+  <si>
+    <t>Floating pin XNC66.noconn(66)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -169,6 +181,15 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -557,7 +578,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -577,7 +598,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -592,7 +613,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -607,17 +628,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -987,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1003,6 +1024,26 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1058,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1027,7 +1068,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1042,7 +1083,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1057,17 +1098,32 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="56">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -156,19 +156,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.VSENSE(105)</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.IREPLICA(100)</t>
-  </si>
-  <si>
-    <t>Floating pin XNC66.noconn(66)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -183,13 +171,10 @@
     <t>No Connects - Inputs</t>
   </si>
   <si>
-    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>tdo - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "tdo", "io": "inout", "bus": "", "type": "node"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -578,7 +563,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -598,7 +583,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -613,7 +598,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -628,17 +613,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1008,7 +993,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1026,44 +1011,69 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1074,59 +1084,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -169,12 +169,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>tdo - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "tdo", "io": "inout", "bus": "", "type": "node"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -563,7 +557,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -583,7 +577,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -598,32 +592,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1073,12 +1067,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -117,34 +117,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XMAIN.CLOCKofftime_0 --&gt; XMAIN.CLOCKofftime_1 --&gt; XMAIN.CLOCKofftime_2 --&gt; XMAIN.CLOCKofftime_3(a0)</t>
-  </si>
-  <si>
-    <t>Shorted input d0 XALGORITHM.enableFAULT --&gt; XALGORITHM.STATEcontrol0 --&gt; XALGORITHM.STATEcontrol1 --&gt; XALGORITHM.STATEcontrol2 --&gt; XALGORITHM.STATEcontrol3(d0)</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XCONTROL.fcm --&gt; XCONTROL.blank_bottom --&gt; XCONTROL.blank_refresh(a0)</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XU21.i0 --&gt; XU22.i0(a0)</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XMAIN.mode_hiccup --&gt; XMAIN.blank_thermal(a0)</t>
-  </si>
-  <si>
-    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
-  </si>
-  <si>
-    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
-  </si>
-  <si>
-    <t>Shorted input d0 XMAIN.STATEcontrol0 --&gt; XMAIN.STATEcontrol1 --&gt; XMAIN.STATEcontrol2 --&gt; XMAIN.STATEcontrol3(d0)</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XMAIN8.halfway --&gt; XMAIN8.softstart_1ms(a0)</t>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
+  </si>
+  <si>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -557,7 +533,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -577,7 +553,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -592,7 +568,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -607,17 +583,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +838,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -872,102 +848,32 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -977,7 +883,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +898,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1002,7 +908,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +923,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1027,7 +933,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1042,7 +948,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1062,7 +968,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -10,22 +10,21 @@
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
     <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
-    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
-    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
-    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
-    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
+    <sheet name="Shorted Nets" sheetId="4" r:id="rId4"/>
+    <sheet name="Floating Inputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Outputs" sheetId="6" r:id="rId6"/>
+    <sheet name="No Connects - Customer" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Celera" sheetId="8" r:id="rId8"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="9" r:id="rId9"/>
+    <sheet name="Ring Core IO check report" sheetId="10" r:id="rId10"/>
+    <sheet name="D to A Tree" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="240">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -114,37 +113,619 @@
     <t>All symbols have nets.</t>
   </si>
   <si>
-    <t>Shorted Inputs</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
-  </si>
-  <si>
-    <t>Shorted Outputs</t>
-  </si>
-  <si>
-    <t>No Shorted Output Nets found.</t>
+    <t>Shorted Nets</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>ERROR: Net a0 - Shorted inputs (XtieLo.q --&gt; Xoscillator.ten --&gt; XSERDEScontrolDRMautoNo.a0 --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2caddress --&gt; XSERDEScontrolDRMautoNo.i2caddress)(a0)</t>
   </si>
   <si>
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraRING</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraRING.tmi(tmi[5])</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU21</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 19 io: output</t>
+  </si>
+  <si>
+    <t>XU11.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XU12.qb net: 28 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU46</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 21 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 29 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU47</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 13 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 17 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU48</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 31 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 35 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 39 io: output</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 43 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU49</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU50</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 111 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 113 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 115 io: output</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 117 io: output</t>
+  </si>
+  <si>
+    <t>XU29.qb net: 119 io: output</t>
+  </si>
+  <si>
+    <t>XU39.qb net: 121 io: output</t>
+  </si>
+  <si>
+    <t>XU67.qb net: 123 io: output</t>
+  </si>
+  <si>
+    <t>XU23.qb net: 125 io: output</t>
+  </si>
+  <si>
+    <t>XU5.qb net: 127 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU51</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>XU14.DRAINk net: 66 io: inout</t>
+  </si>
+  <si>
+    <t>XU5.DRAINk net: 67 io: inout</t>
+  </si>
+  <si>
+    <t>Xfetdriver1.gate_status net: 71 io: output</t>
+  </si>
+  <si>
+    <t>XU16.SOURCEk net: 72 io: inout</t>
+  </si>
+  <si>
+    <t>XU17.ok_cboothv net: 75 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU2</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU26</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU27</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU28</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN,XOK</t>
+  </si>
+  <si>
+    <t>XU12.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_sync net: dft_sync io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_clock net: dft_clock io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.ISLOPECOMP net: ISLOPECOMP io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_synclow net: dft_synclow io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.fault_clock net: fault_clock io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_synchigh net: dft_synchigh io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_clocksync net: dft_clocksync io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_clockstartup net: dft_clockstartup io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_clockinternal net: dft_clockinternal io: </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>XOSCEXT.tdi_osc net: noconn_no_dft_tdi_osc1 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.OFF net: XU89_no_dft_noconn_OFF io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.TOP net: XU96_no_dft_noconn_TOP io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.IDLE net: XU93_no_dft_noconn_IDLE io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.FAULT net: XU91_no_dft_noconn_FAULT io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.READY net: XU92_no_dft_noconn_READY io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.BOTTOM net: XU95_no_dft_noconn_BOTTOM io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.POWERUP net: XU90_no_dft_noconn_POWERUP io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.REFRESH net: XU94_no_dft_noconn_REFRESH io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top3SYNC net: XU14_no_dft_noconn_top3SYNC io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top4SYNC net: XU16_no_dft_noconn_top4SYNC io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top6aSYNC net: XU18_no_dft_noconn_top6aSYNC io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top6bSYNC net: XU20_no_dft_noconn_top6bSYNC io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm0 net: noconn_drm16_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>XU3.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive2 io: output</t>
+  </si>
+  <si>
+    <t>XU9.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive3 io: output</t>
+  </si>
+  <si>
+    <t>XU17.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive4 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.botswineg net: botswineg io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.botswipeak net: botswipeak io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.topswipeak net: topswipeak io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.botswstatus net: botswstatus io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.botswzcross net: botswzcross io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.topswstatus net: topswstatus io: </t>
+  </si>
+  <si>
+    <t>XU22.pulse net: XU12_no_dft_noconn_pulse io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm1 net: noconn_drm24_drm1_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm1 net: noconn_drm24_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>XU22.TAI_ISLOPECOMP net: noconn_no_dft_TAI_ISLOPECOMP6 io: output</t>
+  </si>
+  <si>
+    <t>XU2.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive5 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.fault_run net: fault_run io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.fault_freeze net: fault_freeze io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_delaySHORT net: dft_delaySHORT io: </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_pgout net: dft_pgout io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_pgDELAY net: dft_pgDELAY io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.fault_short net: fault_short io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_REFBUFFER net: dft_REFBUFFER io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_pgSTARTUP net: dft_pgSTARTUP io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_pgDEGLITCH net: dft_pgDEGLITCH io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_shortdelay net: dft_shortdelay io: </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>XU4.tdi_padopendrain net: noconn_no_dft_tdi_padopendrain7 io: output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.REFINT net: REFINT io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.go_driver net: go_driver io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.IREF_DRIVER net: IREF_DRIVER io: </t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XU18.pulse net: XU2_no_dft_noconn_pulse io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm2 net: noconn_drm48_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm3 net: noconn_drm48_drm3_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm4 net: noconn_drm48_drm4_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm5 net: noconn_drm48_drm5_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.OFF net: XU54_no_dft_noconn_OFF io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.RUN net: XU61_no_dft_noconn_RUN io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.FAULT net: XU56_no_dft_noconn_FAULT io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.ENABLE net: XU55_no_dft_noconn_ENABLE io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.UNDEF4 net: XU58_no_dft_noconn_UNDEF4 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.UNDEF5 net: XU59_no_dft_noconn_UNDEF5 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.SOFTSTART net: XU57_no_dft_noconn_SOFTSTART io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.REGULATION net: XU60_no_dft_noconn_REGULATION io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.porb net: porb io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.REF0V9 net: REF0V9 io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.go_vcc net: go_vcc io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.ok_service net: ok_service io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.ok_reference net: ok_reference io: </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm0 net: noconn_drm56_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm0 net: noconn_drm56_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm1 net: noconn_drm56_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_7 io: output</t>
+  </si>
+  <si>
+    <t>XU4.TAI_REF net: noconn_no_dft_TAI_REF8 io: output</t>
+  </si>
+  <si>
+    <t>XU4.TAI_REFBG net: noconn_no_dft_TAI_REFBG9 io: output</t>
+  </si>
+  <si>
+    <t>Xvbias1.TAI_VBIAS net: noconn_no_dft_TAI_VBIAS10 io: output</t>
+  </si>
+  <si>
+    <t>Xvbias1.tdi_vbias net: noconn_no_dft_tdi_vbias11 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.SS net: SS io: </t>
+  </si>
+  <si>
+    <t>XU4.pulse net: XU5_no_dft_noconn_pulse io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE</t>
+  </si>
+  <si>
+    <t>XceleraSERVICE.ok_ibias net: noconn io: output</t>
+  </si>
+  <si>
+    <t>Xoscillator.ok_oscillator net: noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDEScontrolDRMautoNo.otp_loadok net: otp_loadok io: output</t>
+  </si>
+  <si>
+    <t>XSERDEScontrolDRMautoNo.otp_program_done net: otp_program_done io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ</t>
+  </si>
+  <si>
+    <t>XceleraSERDES.unlock net: unlock io: output</t>
+  </si>
+  <si>
+    <t>XceleraSERDES.otp_done net: otp_done io: output</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -528,17 +1109,27 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -548,52 +1139,22 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -848,16 +1409,11 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -868,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -884,6 +1440,16 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -898,12 +1464,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -918,22 +1484,307 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -943,17 +1794,842 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +2644,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="241">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>ERROR: Net a1 - Shorted inputs (XtieHi.q --&gt; XSERDEScontrolDRMautoNo.a1 --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.enable_hardware)(a1)</t>
   </si>
   <si>
     <t>ERROR: Net a0 - Shorted inputs (XtieLo.q --&gt; Xoscillator.ten --&gt; XSERDEScontrolDRMautoNo.a0 --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2caddress --&gt; XSERDEScontrolDRMautoNo.i2caddress)(a0)</t>
@@ -1114,7 +1117,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1129,7 +1132,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -1144,17 +1147,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -1399,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1415,6 +1418,11 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1429,7 +1437,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1439,17 +1447,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1464,17 +1472,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1489,202 +1497,202 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -1694,97 +1702,97 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1799,92 +1807,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -1894,77 +1902,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -1974,27 +1982,27 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -2004,82 +2012,82 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -2089,92 +2097,92 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -2184,82 +2192,82 @@
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -2269,102 +2277,102 @@
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="132" spans="1:1">
@@ -2374,182 +2382,182 @@
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="173" spans="1:1">
@@ -2559,42 +2567,42 @@
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="184" spans="1:1">
@@ -2604,32 +2612,32 @@
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2644,7 +2652,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/WALTZ/project/Post Hopper Run Checks.xlsx
+++ b/WALTZ/project/Post Hopper Run Checks.xlsx
@@ -13,16 +13,18 @@
     <sheet name="Shorted Nets" sheetId="4" r:id="rId4"/>
     <sheet name="Floating Inputs" sheetId="5" r:id="rId5"/>
     <sheet name="Floating Outputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="7" r:id="rId7"/>
-    <sheet name="Ring Core IO check report" sheetId="8" r:id="rId8"/>
-    <sheet name="D to A Tree" sheetId="9" r:id="rId9"/>
+    <sheet name="No Connects - Customer" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Celera" sheetId="8" r:id="rId8"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="9" r:id="rId9"/>
+    <sheet name="Ring Core IO check report" sheetId="10" r:id="rId10"/>
+    <sheet name="D to A Tree" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="240">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -108,49 +110,622 @@
     <t>Missing Nets</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+    <t>All symbols have nets.</t>
+  </si>
+  <si>
+    <t>Shorted Nets</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>ERROR: Net a0 - Shorted inputs (XtieLo.q --&gt; Xoscillator.ten --&gt; XSERDEScontrolDRMautoNo.a0 --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2caddress --&gt; XSERDEScontrolDRMautoNo.i2caddress)(a0)</t>
+  </si>
+  <si>
+    <t>Floating Inputs</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraRING</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraRING.tmi(tmi[5])</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU21</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 19 io: output</t>
+  </si>
+  <si>
+    <t>XU11.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XU12.qb net: 28 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU46</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 21 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 29 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU47</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 13 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 17 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU48</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 31 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 35 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 39 io: output</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 43 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU49</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU50</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 111 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 113 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 115 io: output</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 117 io: output</t>
+  </si>
+  <si>
+    <t>XU29.qb net: 119 io: output</t>
+  </si>
+  <si>
+    <t>XU39.qb net: 121 io: output</t>
+  </si>
+  <si>
+    <t>XU67.qb net: 123 io: output</t>
+  </si>
+  <si>
+    <t>XU23.qb net: 125 io: output</t>
+  </si>
+  <si>
+    <t>XU5.qb net: 127 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU51</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top3SYNC net: 139 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top4SYNC net: 142 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top6aSYNC net: 144 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top6bSYNC net: 146 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.OFF net: 148 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.POWERUP net: 150 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.FAULT net: 152 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.READY net: 154 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.IDLE net: 156 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.REFRESH net: 158 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.BOTTOM net: 162 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.TOP net: 164 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>XU14.DRAINk net: 66 io: inout</t>
+  </si>
+  <si>
+    <t>XU5.DRAINk net: 67 io: inout</t>
+  </si>
+  <si>
+    <t>Xfetdriver1.gate_status net: 71 io: output</t>
+  </si>
+  <si>
+    <t>XU16.SOURCEk net: 72 io: inout</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>XU22.pulse net: 41 io: output</t>
+  </si>
+  <si>
+    <t>XU17.ok_cboothv net: 75 io: output</t>
+  </si>
+  <si>
+    <t>XU18.pulse net: 52 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU2</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU26</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU27</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU28</t>
+  </si>
+  <si>
+    <t>XMAIN.OFF net: 102 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.ENABLE net: 107 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.FAULT net: 110 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.SOFTSTART net: 113 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.UNDEF4 net: 114 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.UNDEF5 net: 115 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.REGULATION net: 116 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.RUN net: 117 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN,XOK</t>
+  </si>
+  <si>
+    <t>XU12.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t>XU4.pulse net: 24 io: output</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_sync net: dft_sync io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_clock net: dft_clock io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.ISLOPECOMP net: ISLOPECOMP io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_synclow net: dft_synclow io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.fault_clock net: fault_clock io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_synchigh net: dft_synchigh io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_clocksync net: dft_clocksync io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_clockstartup net: dft_clockstartup io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_clockinternal net: dft_clockinternal io: input</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>XOSCEXT.tdi_osc net: noconn_no_dft_tdi_osc1 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm0 net: noconn_drm16_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>XU3.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive2 io: output</t>
+  </si>
+  <si>
+    <t>XU9.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive3 io: output</t>
+  </si>
+  <si>
+    <t>XU17.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive4 io: output</t>
+  </si>
+  <si>
+    <t>XDEBUG.botswineg net: botswineg io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.botswipeak net: botswipeak io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.topswipeak net: topswipeak io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.botswstatus net: botswstatus io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.botswzcross net: botswzcross io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.topswstatus net: topswstatus io: input</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm1 net: noconn_drm24_drm1_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm1 net: noconn_drm24_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>XU22.TAI_ISLOPECOMP net: noconn_no_dft_TAI_ISLOPECOMP6 io: output</t>
+  </si>
+  <si>
+    <t>XU2.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive5 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>XDEBUG.fault_run net: fault_run io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.fault_freeze net: fault_freeze io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_delaySHORT net: dft_delaySHORT io: input</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_pgout net: dft_pgout io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_pgDELAY net: dft_pgDELAY io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.fault_short net: fault_short io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_REFBUFFER net: dft_REFBUFFER io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_pgSTARTUP net: dft_pgSTARTUP io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_pgDEGLITCH net: dft_pgDEGLITCH io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_shortdelay net: dft_shortdelay io: input</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>XU4.tdi_padopendrain net: noconn_no_dft_tdi_padopendrain7 io: output</t>
+  </si>
+  <si>
+    <t>XDEBUG.REFINT net: REFINT io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.go_driver net: go_driver io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.IREF_DRIVER net: IREF_DRIVER io: input</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm2 net: noconn_drm48_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm3 net: noconn_drm48_drm3_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm4 net: noconn_drm48_drm4_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm5 net: noconn_drm48_drm5_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>XDEBUG.porb net: porb io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.REF0V9 net: REF0V9 io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.go_vcc net: go_vcc io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.ok_service net: ok_service io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.ok_reference net: ok_reference io: input</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm0 net: noconn_drm56_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm0 net: noconn_drm56_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm1 net: noconn_drm56_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_7 io: output</t>
+  </si>
+  <si>
+    <t>XU4.TAI_REF net: noconn_no_dft_TAI_REF8 io: output</t>
+  </si>
+  <si>
+    <t>XU4.TAI_REFBG net: noconn_no_dft_TAI_REFBG9 io: output</t>
+  </si>
+  <si>
+    <t>Xvbias1.TAI_VBIAS net: noconn_no_dft_TAI_VBIAS10 io: output</t>
+  </si>
+  <si>
+    <t>Xvbias1.tdi_vbias net: noconn_no_dft_tdi_vbias11 io: output</t>
+  </si>
+  <si>
+    <t>XDEBUG.SS net: SS io: input</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_7 io: output</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE</t>
   </si>
   <si>
-    <t>XceleraSERVICE,TAO</t>
-  </si>
-  <si>
-    <t>Shorted Nets</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>ERROR: Net a1 - Shorted inputs (XtieHi.q --&gt; XSERDEScontrolDRMautoNo.a1 --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.enable_hardware)(a1)</t>
-  </si>
-  <si>
-    <t>ERROR: Net a0 - Shorted inputs (XtieLo.q --&gt; XSERDEScontrolDRMautoNo.a0 --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2caddress --&gt; XSERDEScontrolDRMautoNo.i2caddress)(a0)</t>
-  </si>
-  <si>
-    <t>Floating Inputs</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraRING</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraRING.tmi(tmi[5])</t>
-  </si>
-  <si>
-    <t>Floating pin XNCtmi.noconn(tmi)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDRMautoNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDRMautoNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
+    <t>XceleraSERVICE.ok_ibias net: noconn io: output</t>
+  </si>
+  <si>
+    <t>Xoscillator.ok_oscillator net: noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDEScontrolDRMautoNo.otp_loadok net: otp_loadok io: output</t>
+  </si>
+  <si>
+    <t>XSERDEScontrolDRMautoNo.otp_program_done net: otp_program_done io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ</t>
+  </si>
+  <si>
+    <t>XceleraSERDES.unlock net: unlock io: output</t>
+  </si>
+  <si>
+    <t>XceleraSERDES.otp_done net: otp_done io: output</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -532,6 +1107,61 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A50"/>
@@ -744,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -760,16 +1390,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -779,27 +1399,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -809,12 +1424,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -824,37 +1439,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -864,42 +1459,22 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -909,17 +1484,447 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -929,27 +1934,727 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -959,22 +2664,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
